--- a/data/trans_orig/P70D_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P70D_2023-Clase-trans_orig.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W88"/>
+  <dimension ref="A1:W76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su autopercepción de su capacidad laboral actual en 2023</t>
+          <t>Población según su autopercepción de su capacidad laboral actual en 2023 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -728,12 +728,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>107846</t>
+          <t>108422</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>147578</t>
+          <t>150035</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -743,12 +743,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>104842</t>
+          <t>104983</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>134899</t>
+          <t>135127</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>223577</t>
+          <t>223898</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>274871</t>
+          <t>275262</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,19%</t>
         </is>
       </c>
     </row>
@@ -839,12 +839,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79643</t>
+          <t>78023</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>114538</t>
+          <t>114396</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -854,12 +854,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65690</t>
+          <t>65825</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>94049</t>
+          <t>93208</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -889,12 +889,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>154037</t>
+          <t>153390</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>198834</t>
+          <t>198973</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,77%</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87560</t>
+          <t>85429</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>125419</t>
+          <t>121984</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -965,12 +965,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>77008</t>
+          <t>77194</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>105780</t>
+          <t>105272</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1000,12 +1000,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>171349</t>
+          <t>170368</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>217978</t>
+          <t>216889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,45%</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7442</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22685</t>
+          <t>23250</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21972</t>
+          <t>21885</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18388</t>
+          <t>18593</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38294</t>
+          <t>37778</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15664</t>
+          <t>16209</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2797</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10728</t>
+          <t>10729</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6590</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22693</t>
+          <t>22156</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10839</t>
+          <t>8619</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1682</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11294</t>
+          <t>10699</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15662</t>
+          <t>15827</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>839</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>6916</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1520,12 +1520,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3073</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2669</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1616,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3585</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -1727,12 +1727,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2587</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -1838,12 +1838,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1614</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>101482</t>
+          <t>101979</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>137857</t>
+          <t>138506</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2081,12 +2081,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59922</t>
+          <t>60927</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84771</t>
+          <t>87757</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>167610</t>
+          <t>169241</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>214918</t>
+          <t>214976</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,63%</t>
         </is>
       </c>
     </row>
@@ -2177,12 +2177,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63984</t>
+          <t>63733</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>97646</t>
+          <t>99440</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2192,12 +2192,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>71937</t>
+          <t>72173</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>98170</t>
+          <t>98243</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>144161</t>
+          <t>144621</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>187227</t>
+          <t>189528</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>34,06%</t>
         </is>
       </c>
     </row>
@@ -2288,12 +2288,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>63092</t>
+          <t>63086</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>96076</t>
+          <t>96612</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>61386</t>
+          <t>61171</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>87738</t>
+          <t>85661</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>133549</t>
+          <t>132485</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>174458</t>
+          <t>173170</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -2399,12 +2399,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7733</t>
+          <t>7708</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28062</t>
+          <t>30177</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2414,12 +2414,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>9231</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22724</t>
+          <t>21409</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18561</t>
+          <t>19133</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44738</t>
+          <t>45520</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -2510,12 +2510,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4199</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18192</t>
+          <t>17026</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2545,12 +2545,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>8958</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2580,12 +2580,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6759</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22575</t>
+          <t>23061</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2691,12 +2691,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>660</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -2732,12 +2732,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4092</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>4342</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -2843,12 +2843,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -2954,12 +2954,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2969,12 +2969,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3065,12 +3065,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3100,12 +3100,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3115,12 +3115,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3176,12 +3176,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3404,12 +3404,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23820</t>
+          <t>23921</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>209492</t>
+          <t>208711</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3419,12 +3419,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3439,12 +3439,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17322</t>
+          <t>17573</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>31045</t>
+          <t>31563</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3454,12 +3454,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>39908</t>
+          <t>48504</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>226997</t>
+          <t>226291</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,29%</t>
         </is>
       </c>
     </row>
@@ -3515,12 +3515,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>122187</t>
+          <t>122206</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>442836</t>
+          <t>445742</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9350</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20614</t>
+          <t>19810</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>133938</t>
+          <t>134937</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>490956</t>
+          <t>467974</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3600,12 +3600,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>83,31%</t>
         </is>
       </c>
     </row>
@@ -3626,12 +3626,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14090</t>
+          <t>11945</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>116105</t>
+          <t>116468</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3661,12 +3661,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>18493</t>
+          <t>18687</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>32480</t>
+          <t>32811</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>21708</t>
+          <t>28253</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>146959</t>
+          <t>147223</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -3737,12 +3737,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>4098</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>44879</t>
+          <t>43956</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9221</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3807,12 +3807,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6769</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>48756</t>
+          <t>48991</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -3848,12 +3848,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>12890</t>
+          <t>12788</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6413</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>1639</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>16412</t>
+          <t>15717</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>4842</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2351</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4708</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -4070,12 +4070,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5505</t>
+          <t>4580</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -4181,12 +4181,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4196,12 +4196,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -4292,12 +4292,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4362,12 +4362,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3003</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4403,12 +4403,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4473,12 +4473,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3003</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4488,12 +4488,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>8849</t>
+          <t>8898</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>155134</t>
+          <t>152639</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>208978</t>
+          <t>206102</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>123060</t>
+          <t>123350</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>158448</t>
+          <t>159695</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>288938</t>
+          <t>290598</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>352834</t>
+          <t>354171</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,94%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>133082</t>
+          <t>131956</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>183439</t>
+          <t>183989</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>80788</t>
+          <t>80170</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>109634</t>
+          <t>111865</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>225773</t>
+          <t>222962</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>282328</t>
+          <t>280090</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,42%</t>
         </is>
       </c>
     </row>
@@ -4964,12 +4964,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>120664</t>
+          <t>121713</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>166316</t>
+          <t>166527</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -4979,12 +4979,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -4999,12 +4999,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>112895</t>
+          <t>111358</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>143750</t>
+          <t>145254</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>242921</t>
+          <t>242721</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>297563</t>
+          <t>297812</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5049,12 +5049,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,22%</t>
         </is>
       </c>
     </row>
@@ -5075,12 +5075,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>29583</t>
+          <t>28995</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>55786</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>27914</t>
+          <t>28123</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>49559</t>
+          <t>49118</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>62411</t>
+          <t>60596</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>94960</t>
+          <t>95233</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>13843</t>
+          <t>14538</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>33833</t>
+          <t>33971</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>7591</t>
+          <t>7386</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>20104</t>
+          <t>19935</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>24693</t>
+          <t>24419</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>47435</t>
+          <t>48365</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>15415</t>
+          <t>15117</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>14848</t>
+          <t>14632</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>9138</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>23789</t>
+          <t>24379</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>5796</t>
+          <t>5928</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>7412</t>
+          <t>6126</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>846</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>8033</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>6053</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>2223</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>10572</t>
+          <t>11233</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5604,12 +5604,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4678</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>786</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>6822</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4749</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>867</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>8549</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6444</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>776</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>7704</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -6080,12 +6080,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>64941</t>
+          <t>64724</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>98811</t>
+          <t>99878</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6095,12 +6095,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>52785</t>
+          <t>55551</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>168671</t>
+          <t>172747</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>128583</t>
+          <t>123562</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>244514</t>
+          <t>252921</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>41,39%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>40861</t>
+          <t>41756</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>69541</t>
+          <t>69628</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>74521</t>
+          <t>74873</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>243586</t>
+          <t>238776</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>127747</t>
+          <t>125509</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>341804</t>
+          <t>318246</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>52,08%</t>
         </is>
       </c>
     </row>
@@ -6302,12 +6302,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>58032</t>
+          <t>57248</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>93125</t>
+          <t>92402</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6317,12 +6317,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6337,12 +6337,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>48008</t>
+          <t>44756</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>109979</t>
+          <t>109821</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6352,12 +6352,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6372,12 +6372,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>104173</t>
+          <t>105702</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>189115</t>
+          <t>190699</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6387,12 +6387,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>10049</t>
+          <t>10008</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>31395</t>
+          <t>29058</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>13967</t>
+          <t>15361</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>42135</t>
+          <t>41751</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>29792</t>
+          <t>29850</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>63313</t>
+          <t>62491</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -6524,12 +6524,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>14141</t>
+          <t>13202</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6539,12 +6539,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6559,12 +6559,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>4807</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>19670</t>
+          <t>19021</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6594,12 +6594,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>9916</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>27940</t>
+          <t>27114</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -6635,12 +6635,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6650,12 +6650,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>5686</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>34818</t>
+          <t>36023</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>6543</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>33302</t>
+          <t>35665</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>4194</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>693</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>8922</t>
+          <t>8061</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>829</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>124</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>4603</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,02%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -6968,12 +6968,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7003,12 +7003,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>934</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>7752</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7018,12 +7018,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7038,12 +7038,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>961</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>7151</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -7079,12 +7079,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>2842</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>6545</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7225,12 +7225,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7240,12 +7240,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>6471</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -7400,7 +7400,7 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
@@ -7408,107 +7408,107 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>577</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>608126</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>392809</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>713600</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>584</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>456105</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>384465</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>525855</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1064231</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>828423</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1182716</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,96%</t>
         </is>
       </c>
     </row>
@@ -7519,107 +7519,107 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>434</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>699280</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>508043</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1120021</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>505</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>408063</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>342698</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>562700</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>939</t>
         </is>
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1107343</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>890720</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1673633</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,47%</t>
         </is>
       </c>
     </row>
@@ -7630,107 +7630,107 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>448</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>452055</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>300825</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>536098</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>634</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>396986</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>336375</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>435402</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>849041</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>638969</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>940657</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -7741,107 +7741,107 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>109</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>106223</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>69600</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>134540</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>153</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>97655</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>77341</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>116646</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>262</t>
         </is>
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>203877</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>158219</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>238819</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -7852,107 +7852,107 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>48927</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>30706</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>65809</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35200</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24290</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>47171</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>105</t>
         </is>
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>84126</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>60912</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>104802</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -7963,107 +7963,107 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12205</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5714</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21717</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28234</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18645</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46335</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48</t>
         </is>
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>40439</t>
         </is>
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27087</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>62671</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -8074,107 +8074,107 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12489</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5319</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10013</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5446</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17030</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -8185,107 +8185,107 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3492</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8728</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5139</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2477</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10784</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15490</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -8301,102 +8301,102 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2459</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9872</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9827</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -8407,107 +8407,107 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>786</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7496</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>571</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10042</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,3%</t>
         </is>
       </c>
     </row>
@@ -8518,107 +8518,107 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11839</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>771</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4998</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -8631,1462 +8631,123 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1942588</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1942588</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1942588</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1440537</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1440537</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1440537</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3643</t>
         </is>
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3383124</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3383124</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3383124</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>577</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>608126</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>411058</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>711968</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>31,3%</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>21,16%</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>36,65%</t>
-        </is>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>456105</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>391298</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>529356</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr">
-        <is>
-          <t>31,66%</t>
-        </is>
-      </c>
-      <c r="O76" s="2" t="inlineStr">
-        <is>
-          <t>27,16%</t>
-        </is>
-      </c>
-      <c r="P76" s="2" t="inlineStr">
-        <is>
-          <t>36,75%</t>
-        </is>
-      </c>
-      <c r="Q76" s="2" t="inlineStr">
-        <is>
-          <t>1161</t>
-        </is>
-      </c>
-      <c r="R76" s="2" t="inlineStr">
-        <is>
-          <t>1064231</t>
-        </is>
-      </c>
-      <c r="S76" s="2" t="inlineStr">
-        <is>
-          <t>810888</t>
-        </is>
-      </c>
-      <c r="T76" s="2" t="inlineStr">
-        <is>
-          <t>1188060</t>
-        </is>
-      </c>
-      <c r="U76" s="2" t="inlineStr">
-        <is>
-          <t>31,46%</t>
-        </is>
-      </c>
-      <c r="V76" s="2" t="inlineStr">
-        <is>
-          <t>23,97%</t>
-        </is>
-      </c>
-      <c r="W76" s="2" t="inlineStr">
-        <is>
-          <t>35,12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="1" t="n"/>
-      <c r="B77" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>699280</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>507495</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>1106431</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>36,0%</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>26,12%</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>56,96%</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>505</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>408063</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>343039</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>597765</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr">
-        <is>
-          <t>28,33%</t>
-        </is>
-      </c>
-      <c r="O77" s="2" t="inlineStr">
-        <is>
-          <t>23,81%</t>
-        </is>
-      </c>
-      <c r="P77" s="2" t="inlineStr">
-        <is>
-          <t>41,5%</t>
-        </is>
-      </c>
-      <c r="Q77" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
-      <c r="R77" s="2" t="inlineStr">
-        <is>
-          <t>1107343</t>
-        </is>
-      </c>
-      <c r="S77" s="2" t="inlineStr">
-        <is>
-          <t>892641</t>
-        </is>
-      </c>
-      <c r="T77" s="2" t="inlineStr">
-        <is>
-          <t>1726381</t>
-        </is>
-      </c>
-      <c r="U77" s="2" t="inlineStr">
-        <is>
-          <t>32,73%</t>
-        </is>
-      </c>
-      <c r="V77" s="2" t="inlineStr">
-        <is>
-          <t>26,39%</t>
-        </is>
-      </c>
-      <c r="W77" s="2" t="inlineStr">
-        <is>
-          <t>51,03%</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="1" t="n"/>
-      <c r="B78" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>448</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>452055</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>305674</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>528947</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>23,27%</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>15,74%</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>27,23%</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>396986</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>321050</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>435411</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr">
-        <is>
-          <t>27,56%</t>
-        </is>
-      </c>
-      <c r="O78" s="2" t="inlineStr">
-        <is>
-          <t>22,29%</t>
-        </is>
-      </c>
-      <c r="P78" s="2" t="inlineStr">
-        <is>
-          <t>30,23%</t>
-        </is>
-      </c>
-      <c r="Q78" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="R78" s="2" t="inlineStr">
-        <is>
-          <t>849041</t>
-        </is>
-      </c>
-      <c r="S78" s="2" t="inlineStr">
-        <is>
-          <t>629312</t>
-        </is>
-      </c>
-      <c r="T78" s="2" t="inlineStr">
-        <is>
-          <t>941303</t>
-        </is>
-      </c>
-      <c r="U78" s="2" t="inlineStr">
-        <is>
-          <t>25,1%</t>
-        </is>
-      </c>
-      <c r="V78" s="2" t="inlineStr">
-        <is>
-          <t>18,6%</t>
-        </is>
-      </c>
-      <c r="W78" s="2" t="inlineStr">
-        <is>
-          <t>27,82%</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="1" t="n"/>
-      <c r="B79" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>106223</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>67663</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>136929</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>7,05%</t>
-        </is>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>97655</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>77475</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr">
-        <is>
-          <t>115904</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr">
-        <is>
-          <t>6,78%</t>
-        </is>
-      </c>
-      <c r="O79" s="2" t="inlineStr">
-        <is>
-          <t>5,38%</t>
-        </is>
-      </c>
-      <c r="P79" s="2" t="inlineStr">
-        <is>
-          <t>8,05%</t>
-        </is>
-      </c>
-      <c r="Q79" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="R79" s="2" t="inlineStr">
-        <is>
-          <t>203877</t>
-        </is>
-      </c>
-      <c r="S79" s="2" t="inlineStr">
-        <is>
-          <t>155855</t>
-        </is>
-      </c>
-      <c r="T79" s="2" t="inlineStr">
-        <is>
-          <t>238562</t>
-        </is>
-      </c>
-      <c r="U79" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="V79" s="2" t="inlineStr">
-        <is>
-          <t>4,61%</t>
-        </is>
-      </c>
-      <c r="W79" s="2" t="inlineStr">
-        <is>
-          <t>7,05%</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="n"/>
-      <c r="B80" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>48927</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>30820</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>66849</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>35200</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr">
-        <is>
-          <t>25301</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr">
-        <is>
-          <t>46856</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="O80" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="P80" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="Q80" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="R80" s="2" t="inlineStr">
-        <is>
-          <t>84126</t>
-        </is>
-      </c>
-      <c r="S80" s="2" t="inlineStr">
-        <is>
-          <t>62578</t>
-        </is>
-      </c>
-      <c r="T80" s="2" t="inlineStr">
-        <is>
-          <t>105624</t>
-        </is>
-      </c>
-      <c r="U80" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="V80" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
-      <c r="W80" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="1" t="n"/>
-      <c r="B81" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>12205</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>6210</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>21825</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>28234</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>18279</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr">
-        <is>
-          <t>50338</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="O81" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="P81" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="Q81" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="R81" s="2" t="inlineStr">
-        <is>
-          <t>40439</t>
-        </is>
-      </c>
-      <c r="S81" s="2" t="inlineStr">
-        <is>
-          <t>26465</t>
-        </is>
-      </c>
-      <c r="T81" s="2" t="inlineStr">
-        <is>
-          <t>58520</t>
-        </is>
-      </c>
-      <c r="U81" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="V81" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="W81" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="1" t="n"/>
-      <c r="B82" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>4997</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>1768</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>12238</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>5319</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr">
-        <is>
-          <t>2555</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr">
-        <is>
-          <t>10755</t>
-        </is>
-      </c>
-      <c r="N82" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O82" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="P82" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="Q82" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R82" s="2" t="inlineStr">
-        <is>
-          <t>10316</t>
-        </is>
-      </c>
-      <c r="S82" s="2" t="inlineStr">
-        <is>
-          <t>5965</t>
-        </is>
-      </c>
-      <c r="T82" s="2" t="inlineStr">
-        <is>
-          <t>17879</t>
-        </is>
-      </c>
-      <c r="U82" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V82" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="W82" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="1" t="n"/>
-      <c r="B83" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>3492</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>988</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>8212</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>5139</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>2299</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>10768</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="O83" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="P83" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="Q83" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R83" s="2" t="inlineStr">
-        <is>
-          <t>8631</t>
-        </is>
-      </c>
-      <c r="S83" s="2" t="inlineStr">
-        <is>
-          <t>4549</t>
-        </is>
-      </c>
-      <c r="T83" s="2" t="inlineStr">
-        <is>
-          <t>14925</t>
-        </is>
-      </c>
-      <c r="U83" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="V83" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="W83" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="1" t="n"/>
-      <c r="B84" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>2262</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>5041</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr">
-        <is>
-          <t>2120</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr">
-        <is>
-          <t>9696</t>
-        </is>
-      </c>
-      <c r="N84" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O84" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="P84" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="Q84" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R84" s="2" t="inlineStr">
-        <is>
-          <t>5041</t>
-        </is>
-      </c>
-      <c r="S84" s="2" t="inlineStr">
-        <is>
-          <t>2359</t>
-        </is>
-      </c>
-      <c r="T84" s="2" t="inlineStr">
-        <is>
-          <t>9621</t>
-        </is>
-      </c>
-      <c r="U84" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V84" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="W84" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="1" t="n"/>
-      <c r="B85" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>2509</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>6790</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>534</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>5808</t>
-        </is>
-      </c>
-      <c r="N85" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="O85" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="P85" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="Q85" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R85" s="2" t="inlineStr">
-        <is>
-          <t>4532</t>
-        </is>
-      </c>
-      <c r="S85" s="2" t="inlineStr">
-        <is>
-          <t>1904</t>
-        </is>
-      </c>
-      <c r="T85" s="2" t="inlineStr">
-        <is>
-          <t>9989</t>
-        </is>
-      </c>
-      <c r="U85" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="V85" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="W85" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="1" t="n"/>
-      <c r="B86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>4774</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>1104</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>12871</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>771</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr">
-        <is>
-          <t>3400</t>
-        </is>
-      </c>
-      <c r="N86" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="O86" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P86" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="Q86" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R86" s="2" t="inlineStr">
-        <is>
-          <t>5546</t>
-        </is>
-      </c>
-      <c r="S86" s="2" t="inlineStr">
-        <is>
-          <t>1882</t>
-        </is>
-      </c>
-      <c r="T86" s="2" t="inlineStr">
-        <is>
-          <t>12053</t>
-        </is>
-      </c>
-      <c r="U86" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V86" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="W86" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="1" t="n"/>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>1648</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>1942588</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>1942588</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>1942588</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>1440537</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>1440537</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr">
-        <is>
-          <t>1440537</t>
-        </is>
-      </c>
-      <c r="N87" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O87" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P87" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q87" s="2" t="inlineStr">
-        <is>
-          <t>3643</t>
-        </is>
-      </c>
-      <c r="R87" s="2" t="inlineStr">
-        <is>
-          <t>3383124</t>
-        </is>
-      </c>
-      <c r="S87" s="2" t="inlineStr">
-        <is>
-          <t>3383124</t>
-        </is>
-      </c>
-      <c r="T87" s="2" t="inlineStr">
-        <is>
-          <t>3383124</t>
-        </is>
-      </c>
-      <c r="U87" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V87" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W87" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A76" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A16:A27"/>
     <mergeCell ref="A40:A51"/>
     <mergeCell ref="A52:A63"/>
-    <mergeCell ref="A76:A87"/>
     <mergeCell ref="A4:A15"/>
     <mergeCell ref="A64:A75"/>
     <mergeCell ref="A1:B2"/>

--- a/data/trans_orig/P70D_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P70D_2023-Clase-trans_orig.xlsx
@@ -723,32 +723,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>127806</t>
+          <t>136663</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>108422</t>
+          <t>115554</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>150035</t>
+          <t>157965</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -758,32 +758,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>120434</t>
+          <t>127771</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>104983</t>
+          <t>113830</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>135127</t>
+          <t>145211</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -793,32 +793,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>248239</t>
+          <t>264435</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>223898</t>
+          <t>237865</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>275262</t>
+          <t>291917</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>40,51%</t>
         </is>
       </c>
     </row>
@@ -834,32 +834,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>95519</t>
+          <t>104430</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78023</t>
+          <t>86105</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>114396</t>
+          <t>124833</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -869,32 +869,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>79105</t>
+          <t>84603</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65825</t>
+          <t>71315</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>93208</t>
+          <t>100478</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -904,32 +904,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>174624</t>
+          <t>189033</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>153390</t>
+          <t>167220</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>198973</t>
+          <t>217392</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>30,17%</t>
         </is>
       </c>
     </row>
@@ -945,32 +945,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>103539</t>
+          <t>112827</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85429</t>
+          <t>93874</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>121984</t>
+          <t>135380</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -980,32 +980,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>90036</t>
+          <t>96272</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>77194</t>
+          <t>82602</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>105272</t>
+          <t>111495</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1015,32 +1015,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>193575</t>
+          <t>209099</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>170368</t>
+          <t>184866</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>216889</t>
+          <t>232099</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13508</t>
+          <t>16805</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8273</t>
+          <t>9356</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23250</t>
+          <t>28413</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13654</t>
+          <t>15024</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>9552</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21885</t>
+          <t>23899</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>27162</t>
+          <t>31829</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18593</t>
+          <t>22737</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37778</t>
+          <t>45637</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -1167,32 +1167,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6878</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16209</t>
+          <t>16715</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1202,32 +1202,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>5640</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2797</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10729</t>
+          <t>11045</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1237,32 +1237,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>12374</t>
+          <t>12795</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22156</t>
+          <t>23173</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>3177</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8619</t>
+          <t>12506</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1313,32 +1313,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10699</t>
+          <t>12530</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1348,32 +1348,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>7725</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>3419</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15827</t>
+          <t>16384</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>5455</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>890</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>3184</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1459,32 +1459,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>2646</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>817</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6916</t>
+          <t>6668</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2614</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>613</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>613</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>648</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>648</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -1946,17 +1946,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>351913</t>
+          <t>382812</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>351913</t>
+          <t>382812</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>351913</t>
+          <t>382812</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1981,17 +1981,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>316381</t>
+          <t>337833</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>316381</t>
+          <t>337833</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>316381</t>
+          <t>337833</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2016,17 +2016,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>668294</t>
+          <t>720645</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>668294</t>
+          <t>720645</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>668294</t>
+          <t>720645</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2061,32 +2061,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>119708</t>
+          <t>126818</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>101979</t>
+          <t>108134</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>138506</t>
+          <t>146702</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2096,32 +2096,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>72831</t>
+          <t>79564</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60927</t>
+          <t>65686</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>87757</t>
+          <t>93037</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2131,32 +2131,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>192539</t>
+          <t>206382</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>169241</t>
+          <t>183288</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>214976</t>
+          <t>230627</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,79%</t>
         </is>
       </c>
     </row>
@@ -2172,32 +2172,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>80587</t>
+          <t>84059</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63733</t>
+          <t>67538</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>99440</t>
+          <t>101934</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2207,32 +2207,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>84416</t>
+          <t>91623</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>72173</t>
+          <t>77783</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>98243</t>
+          <t>106229</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2242,32 +2242,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>165002</t>
+          <t>175682</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>144621</t>
+          <t>153086</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>189528</t>
+          <t>197460</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,21%</t>
         </is>
       </c>
     </row>
@@ -2283,32 +2283,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>79486</t>
+          <t>83376</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>63086</t>
+          <t>66954</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>96612</t>
+          <t>102829</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2318,32 +2318,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>73341</t>
+          <t>77908</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>61171</t>
+          <t>65283</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>85661</t>
+          <t>91364</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2353,32 +2353,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>152828</t>
+          <t>161284</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>132485</t>
+          <t>141485</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>173170</t>
+          <t>183435</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>30,85%</t>
         </is>
       </c>
     </row>
@@ -2394,32 +2394,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15226</t>
+          <t>17512</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7708</t>
+          <t>9460</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30177</t>
+          <t>34039</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2429,32 +2429,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13833</t>
+          <t>15216</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9231</t>
+          <t>9586</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21409</t>
+          <t>21945</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2464,32 +2464,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>29059</t>
+          <t>32727</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19133</t>
+          <t>22349</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45520</t>
+          <t>47790</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -2505,32 +2505,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>8565</t>
+          <t>9214</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17026</t>
+          <t>19323</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2540,32 +2540,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>4740</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8958</t>
+          <t>10352</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2575,32 +2575,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>12596</t>
+          <t>13953</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6912</t>
+          <t>7979</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23061</t>
+          <t>24560</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>781</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>3919</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1634</t>
+          <t>1667</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2661,12 +2661,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5952</t>
+          <t>6053</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2686,22 +2686,22 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>693</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2772,12 +2772,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4342</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>657</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2883,12 +2883,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>657</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3762</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -3284,17 +3284,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>304376</t>
+          <t>321760</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>304376</t>
+          <t>321760</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>304376</t>
+          <t>321760</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3319,17 +3319,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>252085</t>
+          <t>272853</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>252085</t>
+          <t>272853</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>252085</t>
+          <t>272853</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3354,17 +3354,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>556461</t>
+          <t>594612</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>556461</t>
+          <t>594612</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>556461</t>
+          <t>594612</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3399,32 +3399,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>99398</t>
+          <t>111778</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23921</t>
+          <t>94871</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>208711</t>
+          <t>131056</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3434,32 +3434,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>24001</t>
+          <t>26480</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17573</t>
+          <t>19619</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>31563</t>
+          <t>35329</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>123399</t>
+          <t>138258</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>48504</t>
+          <t>121073</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>226291</t>
+          <t>157356</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>44,44%</t>
         </is>
       </c>
     </row>
@@ -3510,32 +3510,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>310205</t>
+          <t>74315</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>122206</t>
+          <t>58972</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>445742</t>
+          <t>90339</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3545,32 +3545,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>13829</t>
+          <t>15753</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8771</t>
+          <t>10396</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>19810</t>
+          <t>22694</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3580,32 +3580,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>324034</t>
+          <t>90068</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>134937</t>
+          <t>74179</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>467974</t>
+          <t>106923</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>30,2%</t>
         </is>
       </c>
     </row>
@@ -3621,32 +3621,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>53304</t>
+          <t>56525</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>11945</t>
+          <t>42794</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>116468</t>
+          <t>72149</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3656,32 +3656,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>25056</t>
+          <t>29232</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>18687</t>
+          <t>21914</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>32811</t>
+          <t>37981</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3691,32 +3691,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>78360</t>
+          <t>85758</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>28253</t>
+          <t>71116</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>147223</t>
+          <t>103172</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>29,14%</t>
         </is>
       </c>
     </row>
@@ -3732,32 +3732,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>18918</t>
+          <t>21836</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4098</t>
+          <t>13045</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>43956</t>
+          <t>36317</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3767,32 +3767,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>5844</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9489</t>
+          <t>10983</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3802,32 +3802,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>23837</t>
+          <t>27680</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>17619</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>48991</t>
+          <t>41152</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -3843,32 +3843,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>12788</t>
+          <t>10092</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3878,32 +3878,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1126</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3913,32 +3913,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>7298</t>
+          <t>7510</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>15717</t>
+          <t>13528</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>781</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4842</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>482</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2338</t>
+          <t>2362</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4110,12 +4110,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>771</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>771</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
@@ -4256,12 +4256,12 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>4446</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1474</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>8898</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1474</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
@@ -4589,12 +4589,12 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8781</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -4622,17 +4622,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>488488</t>
+          <t>271109</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>488488</t>
+          <t>271109</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>488488</t>
+          <t>271109</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4657,17 +4657,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>73212</t>
+          <t>82970</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>73212</t>
+          <t>82970</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>73212</t>
+          <t>82970</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4692,17 +4692,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>561700</t>
+          <t>354079</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>561700</t>
+          <t>354079</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>561700</t>
+          <t>354079</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4737,32 +4737,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>179657</t>
+          <t>200662</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>152639</t>
+          <t>174483</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>206102</t>
+          <t>227776</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4772,32 +4772,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>141323</t>
+          <t>158191</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>123350</t>
+          <t>139007</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>159695</t>
+          <t>177793</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4807,32 +4807,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>320979</t>
+          <t>358854</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>290598</t>
+          <t>326356</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>354171</t>
+          <t>389820</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,49%</t>
         </is>
       </c>
     </row>
@@ -4848,32 +4848,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>158109</t>
+          <t>171357</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>131956</t>
+          <t>146434</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>183989</t>
+          <t>199555</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>94495</t>
+          <t>103586</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>80170</t>
+          <t>89486</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>111865</t>
+          <t>119689</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4918,32 +4918,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>252604</t>
+          <t>274943</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>222962</t>
+          <t>247555</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>280090</t>
+          <t>309506</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -4959,32 +4959,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>142380</t>
+          <t>156758</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>121713</t>
+          <t>133069</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>166527</t>
+          <t>181537</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -4994,32 +4994,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>127859</t>
+          <t>149013</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>111358</t>
+          <t>132391</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>145254</t>
+          <t>166811</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5029,32 +5029,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>270240</t>
+          <t>305771</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>242721</t>
+          <t>274759</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>297812</t>
+          <t>338507</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,82%</t>
         </is>
       </c>
     </row>
@@ -5070,32 +5070,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>40762</t>
+          <t>51363</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>28995</t>
+          <t>38195</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>67787</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5105,32 +5105,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>36995</t>
+          <t>40313</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>28123</t>
+          <t>30433</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>49118</t>
+          <t>52019</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5140,32 +5140,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>77757</t>
+          <t>91676</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>60596</t>
+          <t>74229</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>95233</t>
+          <t>111916</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -5181,32 +5181,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>21959</t>
+          <t>23447</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>14538</t>
+          <t>13731</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>33971</t>
+          <t>34934</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5216,32 +5216,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>12483</t>
+          <t>12892</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>7386</t>
+          <t>7930</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>19935</t>
+          <t>20225</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5251,32 +5251,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>34442</t>
+          <t>36339</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>24419</t>
+          <t>25623</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>48365</t>
+          <t>48208</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -5292,32 +5292,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>7793</t>
+          <t>8004</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>3722</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>15117</t>
+          <t>16466</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5327,32 +5327,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>7381</t>
+          <t>8488</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>3611</t>
+          <t>4031</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>14632</t>
+          <t>16530</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5362,32 +5362,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>15175</t>
+          <t>16492</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>9894</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>24379</t>
+          <t>27382</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5413,12 +5413,12 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>645</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -5448,12 +5448,12 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>1792</t>
+          <t>1788</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
@@ -5483,12 +5483,12 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>6978</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -5514,32 +5514,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>3328</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>860</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>8033</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>6053</t>
+          <t>5837</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5584,32 +5584,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>1819</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>11233</t>
+          <t>11420</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>4733</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,37%</t>
         </is>
       </c>
     </row>
@@ -5736,32 +5736,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>745</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>6822</t>
+          <t>6565</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5771,67 +5771,67 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>4229</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>3289</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
           <t>842</t>
         </is>
       </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>5083</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="inlineStr">
-        <is>
-          <t>3351</t>
-        </is>
-      </c>
-      <c r="S49" s="2" t="inlineStr">
-        <is>
-          <t>867</t>
-        </is>
-      </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>8549</t>
+          <t>8144</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -5857,12 +5857,12 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>6444</t>
+          <t>7391</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>768</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>4438</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -5917,32 +5917,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>2747</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>768</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>7704</t>
+          <t>7734</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -5960,17 +5960,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>559630</t>
+          <t>620532</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>559630</t>
+          <t>620532</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>559630</t>
+          <t>620532</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -5995,17 +5995,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>425921</t>
+          <t>477895</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>425921</t>
+          <t>477895</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>425921</t>
+          <t>477895</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6030,17 +6030,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>985551</t>
+          <t>1098428</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>985551</t>
+          <t>1098428</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>985551</t>
+          <t>1098428</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6075,32 +6075,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>81557</t>
+          <t>108735</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>64724</t>
+          <t>88578</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>99878</t>
+          <t>129725</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6110,32 +6110,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>97518</t>
+          <t>77291</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>55551</t>
+          <t>62967</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>172747</t>
+          <t>91336</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6145,32 +6145,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>179075</t>
+          <t>186027</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>123562</t>
+          <t>162186</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>252921</t>
+          <t>209601</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -6186,32 +6186,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>54861</t>
+          <t>70723</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>41756</t>
+          <t>55278</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>69628</t>
+          <t>87921</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6221,32 +6221,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>136218</t>
+          <t>75308</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>74873</t>
+          <t>62899</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>238776</t>
+          <t>88813</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6256,32 +6256,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>191079</t>
+          <t>146032</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>125509</t>
+          <t>123287</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>318246</t>
+          <t>168220</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>27,14%</t>
         </is>
       </c>
     </row>
@@ -6297,32 +6297,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>73345</t>
+          <t>90506</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>57248</t>
+          <t>73386</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>92402</t>
+          <t>110187</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6332,32 +6332,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>80693</t>
+          <t>97445</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>44756</t>
+          <t>83326</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>109821</t>
+          <t>113512</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6367,32 +6367,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>154039</t>
+          <t>187951</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>105702</t>
+          <t>163714</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>190699</t>
+          <t>212371</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>34,26%</t>
         </is>
       </c>
     </row>
@@ -6408,17 +6408,17 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>17809</t>
+          <t>22963</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>10008</t>
+          <t>13469</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>29058</t>
+          <t>36198</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6443,32 +6443,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>28253</t>
+          <t>30443</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>15361</t>
+          <t>22037</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>41751</t>
+          <t>40774</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6478,32 +6478,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>46062</t>
+          <t>53407</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>29850</t>
+          <t>41420</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>62491</t>
+          <t>71338</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -6519,32 +6519,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>9591</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>13202</t>
+          <t>16845</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6554,32 +6554,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>10276</t>
+          <t>13741</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>19021</t>
+          <t>23410</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6589,32 +6589,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>17416</t>
+          <t>23332</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>10180</t>
+          <t>15117</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>27114</t>
+          <t>34574</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -6665,32 +6665,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>13836</t>
+          <t>12438</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>36023</t>
+          <t>19879</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6700,32 +6700,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>13836</t>
+          <t>12438</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>35665</t>
+          <t>20111</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>6828</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -6786,12 +6786,12 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6811,32 +6811,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3459</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>8793</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>872</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -6862,12 +6862,12 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -6877,77 +6877,77 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>1272</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>4999</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>2145</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>6024</t>
+        </is>
+      </c>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>1210</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t>4636</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O59" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P59" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="Q59" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R59" s="2" t="inlineStr">
-        <is>
-          <t>1373</t>
-        </is>
-      </c>
-      <c r="S59" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="T59" s="2" t="inlineStr">
-        <is>
-          <t>4367</t>
-        </is>
-      </c>
-      <c r="U59" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -6998,32 +6998,32 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>7752</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7033,17 +7033,17 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>556</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>556</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>2842</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -7185,7 +7185,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>8356</t>
+          <t>6949</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>7419</t>
+          <t>5823</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -7298,17 +7298,17 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>238180</t>
+          <t>306841</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>238180</t>
+          <t>306841</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>238180</t>
+          <t>306841</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7333,17 +7333,17 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>372938</t>
+          <t>312968</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>372938</t>
+          <t>312968</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>372938</t>
+          <t>312968</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>611118</t>
+          <t>619810</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>611118</t>
+          <t>619810</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>611118</t>
+          <t>619810</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7413,32 +7413,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>608126</t>
+          <t>684658</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>392809</t>
+          <t>636830</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>713600</t>
+          <t>732362</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7448,32 +7448,32 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>456105</t>
+          <t>469298</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>384465</t>
+          <t>436246</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>525855</t>
+          <t>503708</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7483,32 +7483,32 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>1064231</t>
+          <t>1153956</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>828423</t>
+          <t>1099089</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>1182716</t>
+          <t>1211733</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,77%</t>
         </is>
       </c>
     </row>
@@ -7524,32 +7524,32 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>699280</t>
+          <t>504885</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>508043</t>
+          <t>461520</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>1120021</t>
+          <t>547764</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7559,32 +7559,32 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>408063</t>
+          <t>370873</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>342698</t>
+          <t>341168</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>562700</t>
+          <t>405781</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7594,32 +7594,32 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>1107343</t>
+          <t>875758</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>890720</t>
+          <t>826701</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>1673633</t>
+          <t>930129</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>27,46%</t>
         </is>
       </c>
     </row>
@@ -7635,32 +7635,32 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>452055</t>
+          <t>499993</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>300825</t>
+          <t>457204</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>536098</t>
+          <t>547179</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7670,32 +7670,32 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>396986</t>
+          <t>449870</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>336375</t>
+          <t>418774</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>435402</t>
+          <t>483709</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7705,32 +7705,32 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>849041</t>
+          <t>949863</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>638969</t>
+          <t>892384</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>940657</t>
+          <t>1004511</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>29,65%</t>
         </is>
       </c>
     </row>
@@ -7746,32 +7746,32 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>106223</t>
+          <t>130479</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>69600</t>
+          <t>105072</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>134540</t>
+          <t>157448</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>97655</t>
+          <t>106840</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>77341</t>
+          <t>90762</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>116646</t>
+          <t>125743</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7816,32 +7816,32 @@
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>203877</t>
+          <t>237320</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>158219</t>
+          <t>206613</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>238819</t>
+          <t>270336</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -7857,32 +7857,32 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>48927</t>
+          <t>53848</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>30706</t>
+          <t>40800</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>65809</t>
+          <t>70680</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -7892,32 +7892,32 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>35200</t>
+          <t>40082</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>24290</t>
+          <t>30315</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>47171</t>
+          <t>53825</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -7927,32 +7927,32 @@
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>84126</t>
+          <t>93930</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>60912</t>
+          <t>75087</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>104802</t>
+          <t>113066</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -7968,27 +7968,27 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>12205</t>
+          <t>12742</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>5714</t>
+          <t>6689</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>21717</t>
+          <t>21402</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -8003,32 +8003,32 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>28234</t>
+          <t>28298</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>18645</t>
+          <t>20168</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>46335</t>
+          <t>40362</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8038,32 +8038,32 @@
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>40439</t>
+          <t>41040</t>
         </is>
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>27087</t>
+          <t>29884</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>62671</t>
+          <t>53955</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -8079,17 +8079,17 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>12489</t>
+          <t>11513</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8114,67 +8114,67 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5694</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>10013</t>
+          <t>10329</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>10710</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>5847</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>17800</t>
+        </is>
+      </c>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="P70" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="Q70" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R70" s="2" t="inlineStr">
-        <is>
-          <t>10316</t>
-        </is>
-      </c>
-      <c r="S70" s="2" t="inlineStr">
-        <is>
-          <t>5446</t>
-        </is>
-      </c>
-      <c r="T70" s="2" t="inlineStr">
-        <is>
-          <t>17030</t>
-        </is>
-      </c>
-      <c r="U70" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V70" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -8190,67 +8190,67 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>8728</t>
+          <t>9160</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>5671</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>2746</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>11655</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>5139</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>2477</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t>10784</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="O71" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8260,32 +8260,32 @@
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>8631</t>
+          <t>9906</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>15490</t>
+          <t>17375</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -8336,32 +8336,32 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t>2342</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>9872</t>
+          <t>9704</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8371,17 +8371,17 @@
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>2384</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>9827</t>
+          <t>9870</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8412,17 +8412,17 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>763</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>6668</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8447,17 +8447,17 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>559</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>5776</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8482,17 +8482,17 @@
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>10042</t>
+          <t>9540</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -8523,17 +8523,17 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>11839</t>
+          <t>11701</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>768</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -8568,7 +8568,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>4998</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8593,17 +8593,17 @@
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>5523</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>12346</t>
+          <t>12997</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8613,12 +8613,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -8636,17 +8636,17 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>1942588</t>
+          <t>1903055</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>1942588</t>
+          <t>1903055</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>1942588</t>
+          <t>1903055</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -8671,17 +8671,17 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>1440537</t>
+          <t>1484519</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>1440537</t>
+          <t>1484519</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>1440537</t>
+          <t>1484519</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -8706,17 +8706,17 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>3383124</t>
+          <t>3387574</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>3383124</t>
+          <t>3387574</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>3383124</t>
+          <t>3387574</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
